--- a/Result/profitability/4167.xlsx
+++ b/Result/profitability/4167.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00874999999999998</v>
+        <v>0.28375</v>
       </c>
       <c r="N2" t="n">
-        <v>30.93875</v>
+        <v>30.8575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10375</v>
+        <v>0.16875</v>
       </c>
       <c r="N3" t="n">
-        <v>23.8775</v>
+        <v>24.76125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -7927,6 +7927,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>286</v>
+      </c>
+      <c r="D60" t="n">
+        <v>181</v>
+      </c>
+      <c r="E60" t="n">
+        <v>105</v>
+      </c>
+      <c r="F60" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="G60" t="n">
+        <v>16</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5.53%</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>768</v>
+      </c>
+      <c r="J60" t="n">
+        <v>784</v>
+      </c>
+      <c r="K60" t="n">
+        <v>773</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.5762499999999999</v>
+      </c>
+      <c r="N60" t="n">
+        <v>34.465</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X60" t="n">
+        <v>7.03448275862069</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5.700000000000003</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.1840490797546013</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>-47.6</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>-1.559999999999995</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>-0.04080565001307856</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
